--- a/public/exports-from-60/29189900.xlsx
+++ b/public/exports-from-60/29189900.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">

--- a/public/exports-from-60/29189900.xlsx
+++ b/public/exports-from-60/29189900.xlsx
@@ -8914,7 +8914,7 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">200056978</t>
+          <t xml:space="preserve">200056974</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -54514,7 +54514,7 @@
       </c>
       <c r="K727" t="inlineStr">
         <is>
-          <t xml:space="preserve">311914906</t>
+          <t xml:space="preserve">311914896</t>
         </is>
       </c>
       <c r="L727" t="inlineStr">
@@ -54589,7 +54589,7 @@
       </c>
       <c r="K728" t="inlineStr">
         <is>
-          <t xml:space="preserve">311914906</t>
+          <t xml:space="preserve">311914896</t>
         </is>
       </c>
       <c r="L728" t="inlineStr">
